--- a/AAII_Financials/Quarterly/ADP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ADP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>ADP</t>
   </si>
@@ -656,544 +656,557 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5473800</v>
+      </c>
+      <c r="E8" s="3">
         <v>5939200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5359300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5175200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5126800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5553000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5048400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4832700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4768500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5253800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4668000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4512400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4477800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4927800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4391000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4215600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4127700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4513000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4025400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3832300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3737000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4102000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3695700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3470700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3376800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4047800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3669500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3495700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3479300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3828200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3492400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3310300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3316200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3693000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3238300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3077200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3064900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3410800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2987300</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2916900</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2840000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2949900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2766800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2712800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2695500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2781800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2615600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2518400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2520600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2649200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2442000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2394100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2370900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2508400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2443200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2386100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2379700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2506000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2333500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2216400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2199500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2272200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2115700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2029400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2063000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2234800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2089300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2040000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1996600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2247700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2000200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1927600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1716000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1844700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1709200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1630700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1622700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1701500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1560400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1531500</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2633800</v>
+      </c>
+      <c r="E10" s="3">
         <v>2989300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2592500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2462400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2431300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2771200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2432800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2314300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2247900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2604600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2226000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2118300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2106900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2419400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1947800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1829500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1748000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2007000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1691900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1615900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1537500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1829800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1580000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1441300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1313800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1813000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1580200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1455700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1482700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1580500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1492200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1382700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1600200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1848300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1529100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1446500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1442200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1709300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1426900</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1385400</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1236,130 +1249,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>265900</v>
+      </c>
+      <c r="E12" s="3">
         <v>253900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>257800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>251200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>269400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>247100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>239500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>232600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>247900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>242700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>228700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>236500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>222200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>208600</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>7500</v>
       </c>
       <c r="R12" s="3">
         <v>7500</v>
       </c>
       <c r="S12" s="3">
-        <v>6200</v>
+        <v>7500</v>
       </c>
       <c r="T12" s="3">
         <v>6200</v>
       </c>
       <c r="U12" s="3">
+        <v>6200</v>
+      </c>
+      <c r="V12" s="3">
         <v>7700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>6700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>4900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>4300</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>4800</v>
       </c>
       <c r="AD12" s="3">
         <v>4800</v>
       </c>
       <c r="AE12" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AF12" s="3">
         <v>4500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>5000</v>
-      </c>
-      <c r="AG12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AH12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AI12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ12" s="3">
         <v>153900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>162500</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>159400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>158200</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>166900</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>153300</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>152500</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>154900</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1480,175 +1497,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1500</v>
       </c>
-      <c r="G14" s="3">
-        <v>-2100</v>
-      </c>
       <c r="H14" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-3300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-12700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>900</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>18700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4300</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>12300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>29900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-23800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>12700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>11000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-9400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-7700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>7700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>311000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>13100</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>-3700</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
       <c r="AN14" s="3">
         <v>0</v>
       </c>
       <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
         <v>-205400</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E15" s="3">
         <v>122100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>122900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>123300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>121400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>122400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>126900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>115300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>111000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>119000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>119600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>121300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>114400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>115400</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1701,31 +1724,34 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>72400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>70200</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>69300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>62600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>57800</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>56200</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>54900</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>57200</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1765,252 +1791,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>4189700</v>
+      </c>
+      <c r="E17" s="3">
         <v>4146500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3950700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3835300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3912500</v>
       </c>
       <c r="H17" s="3">
         <v>3912100</v>
       </c>
       <c r="I17" s="3">
+        <v>3912100</v>
+      </c>
+      <c r="J17" s="3">
         <v>3740800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3552600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3662300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3700700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3475600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3387200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3428200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3548700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3306400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3194200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3318800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3334000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3123500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2941800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3058500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3043700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2880400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2718100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2862600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2995700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2848400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2771300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2853300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2843000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2745400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2653600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3055900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2832500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2645000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2510500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2677000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2576000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2203200</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2391300</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1284100</v>
+      </c>
+      <c r="E18" s="3">
         <v>1792700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1408600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1339900</v>
       </c>
-      <c r="G18" s="3">
-        <v>1214300</v>
-      </c>
       <c r="H18" s="3">
+        <v>1214700</v>
+      </c>
+      <c r="I18" s="3">
         <v>1640900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1307600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1280100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1106200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1553100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1192400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1125200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1049600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1379100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1084600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1021400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>808900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1179000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>901900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>890500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>678500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1058300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>815300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>752600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>514200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1052100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>821100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>724400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>626000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>985200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>747000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>656700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>260300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>860500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>593300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>566700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>387900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>834800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>784100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>525600</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2053,8 +2086,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -2097,574 +2131,589 @@
       <c r="P20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R20" s="3">
         <v>30500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>39800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>21100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>29300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>26600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>28800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>35900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>21400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>31200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>27700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>32700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>44600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>46000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>54600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>41000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>21000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>32600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>26000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>23200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>10700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>21700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>26200</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>23300</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>9900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>22600</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>1406600</v>
+      </c>
+      <c r="E21" s="3">
         <v>1914800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1531500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1463200</v>
       </c>
-      <c r="G21" s="3">
-        <v>1335700</v>
-      </c>
       <c r="H21" s="3">
+        <v>1336100</v>
+      </c>
+      <c r="I21" s="3">
         <v>1763300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1434500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1395400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1217200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1672100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1312000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1246500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1164000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1494500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1251900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1196300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>960500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1337300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1055000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1048400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>840400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1206600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>973200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>911400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>671400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1217300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>984700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>896300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>776400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1109300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>877100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>781700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>382800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>967500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>709800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>680100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>493700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>922300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>885100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>626200</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E22" s="3">
         <v>78700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>124100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>135400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>113700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>74800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>129600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>137800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>102200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>62700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>104900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>91600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>106900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>38300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>57000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>51200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>26600</v>
-      </c>
-      <c r="T22" s="3">
-        <v>18400</v>
       </c>
       <c r="U22" s="3">
         <v>18400</v>
       </c>
       <c r="V22" s="3">
+        <v>18400</v>
+      </c>
+      <c r="W22" s="3">
         <v>18500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>17300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>13500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>13900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>15100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>15600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>20000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>31600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>39900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>33700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>21700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>38600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>35900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>28600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>18600</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>27500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>28000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>22800</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>16800</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>20500</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1257800</v>
+      </c>
+      <c r="E23" s="3">
         <v>1781800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1383200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1307500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1190700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1621900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1261300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1236200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1089300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1546300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1143800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1092800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1005600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1364000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1058100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1010000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>803400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1189900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>910100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>900800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>697100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1066200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>832600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>765200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>531300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1076700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>835500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>739100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>633300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>984500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>741000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>646800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>254900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>852600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>587500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>564900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>388400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>827900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>786200</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>528700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>279200</v>
+      </c>
+      <c r="E24" s="3">
         <v>422000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>321200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>294500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>280000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>372400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>298100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>279900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>260000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>361400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>265400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>233400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>228900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>320900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>245000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>231000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>177900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>261400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>215700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>158900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>255500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>185100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>163100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>126000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>255800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>183900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>156700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>157900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>230800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>183400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>140300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>158900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>206700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>149700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>152300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>122600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>240000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>275300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>160000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2785,252 +2834,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>978600</v>
+      </c>
+      <c r="E26" s="3">
         <v>1359800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1062000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1013000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>910700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1249500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>963200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>956300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>829300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1184900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>878400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>859400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>776700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1043100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>813100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>779000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>625500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>928500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>694400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>700500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>538200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>810700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>647500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>602100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>405300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>820900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>651600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>582400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>475400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>753700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>557600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>506500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>96000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>645900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>437800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>412600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>265800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>587900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>510900</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>368700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>978600</v>
+      </c>
+      <c r="E27" s="3">
         <v>1359800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1062000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1013000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>910700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1249500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>963200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>956300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>829300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1184900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>878400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>859400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>776700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1043100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>813100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>779000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>625500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>928500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>694400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>700500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>538200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>810700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>647500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>602100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>405300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>820900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>651600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>582400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>475400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>753700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>557600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>506500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>96000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>645900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>437800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>412600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>265800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>587900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>510900</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>368700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3151,8 +3209,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3207,8 +3268,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>24</v>
@@ -3225,15 +3286,15 @@
       <c r="Z29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AB29" s="3">
         <v>6300</v>
       </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
@@ -3244,26 +3305,26 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>600</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>44900</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>232600</v>
       </c>
-      <c r="AL29" s="3" t="s">
+      <c r="AM29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AM29" s="3">
-        <v>0</v>
-      </c>
       <c r="AN29" s="3">
         <v>0</v>
       </c>
@@ -3273,8 +3334,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3395,8 +3459,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3517,8 +3584,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3561,208 +3631,214 @@
       <c r="P32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R32" s="3">
         <v>-30500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-39800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-21100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-29300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-26600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-28800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-35900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-21400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-31200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-27700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-32700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-44600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-46000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-54600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-41000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-32600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-26000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-23200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-10700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-21700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-26200</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-23300</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-9900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-22600</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-23000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>978600</v>
+      </c>
+      <c r="E33" s="3">
         <v>1359800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1062000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1013000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>910700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1249500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>963200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>956300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>829300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1184900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>878400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>859400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>776700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1043100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>813100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>779000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>625500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>928500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>694400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>700500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>538200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>810700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>647500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>602100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>411600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>820900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>651600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>582400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>475400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>753700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>558200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>505400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>140900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>643100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>670400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>412600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>265800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>587900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>510900</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>368700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3883,257 +3959,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>978600</v>
+      </c>
+      <c r="E35" s="3">
         <v>1359800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1062000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1013000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>910700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1249500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>963200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>956300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>829300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1184900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>878400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>859400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>776700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1043100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>813100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>779000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>625500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>928500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>694400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>700500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>538200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>810700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>647500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>602100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>411600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>820900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>651600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>582400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>475400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>753700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>558200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>505400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>140900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>643100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>670400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>412600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>265800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>587900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>510900</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>368700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4176,8 +4261,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4220,130 +4306,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4230100</v>
+      </c>
+      <c r="E41" s="3">
         <v>3228400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2424700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2478000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3347800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2680600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2216400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2104900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2913400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3291700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1641300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1441400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2083500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1828400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1345000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1207700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1436300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1634200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1745000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1602100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2575200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1891500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1602200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1613100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1908500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1705000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1500400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1403900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1949200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1826200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2785600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1490300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2170000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2293600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1773400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2363600</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2780400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2995500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2705200</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2776600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4354,240 +4444,246 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>5218700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4460400</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>4663600</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>24400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>14900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>14700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>26300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>16400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>24400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>47000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>27600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>19700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>74300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>10400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>10500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>10600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3400</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
-      </c>
       <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
         <v>3200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>7200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3545100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>10500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>7300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>127100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ42" s="3">
-        <v>0</v>
-      </c>
       <c r="AK42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="3">
         <v>3200</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>113200</v>
-      </c>
-      <c r="AM42" s="3">
-        <v>3200</v>
       </c>
       <c r="AN42" s="3">
         <v>3200</v>
       </c>
       <c r="AO42" s="3">
-        <v>41000</v>
+        <v>3200</v>
       </c>
       <c r="AP42" s="3">
         <v>41000</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>41000</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3521100</v>
+      </c>
+      <c r="E43" s="3">
         <v>3569200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3408500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3463600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3579100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3547900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3503500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3316700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3428200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3460700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3372400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3095100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3009600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3072100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3162300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2939200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3170600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3250700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2736000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2769700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2727400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2765400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2509800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2489100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2441300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2620600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2587900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2490400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2439300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2485200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2638100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2216400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1984200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2043400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2045500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1788700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1703600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1811500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1839500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1620600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4630,8 +4726,8 @@
       <c r="P44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4708,257 +4804,266 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>44809900</v>
+      </c>
+      <c r="E45" s="3">
         <v>47436500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>68638900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33042200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>31864900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>40308300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>48534500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>29826000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>39200900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>48887200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>43505300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>35928700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37062800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>46591400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>41619900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>33797500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>50151000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>58991300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>46606600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>47601800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>35428800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>42085000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>37539700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>30709800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>27214300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>31379900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>37269500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>22069100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>29943300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>36605300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>26255500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>26122100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>27665800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>34377000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>35527900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>26737100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>28171500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>34704200</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>31222400</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>25686000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>52561100</v>
+      </c>
+      <c r="E46" s="3">
         <v>54234100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>74472100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>44202500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>43252200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>46536800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>54254400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>39911200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>45542500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>55639600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>48543400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>40480100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>42170600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>51518200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>46143600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>37968800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>54804900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>63903800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>51107300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>52047900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>40741800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>46752400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>41662300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>34815400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>31564100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>35708700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>41365000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>29508500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>34342300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>40924000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>31682600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>29955900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>31823300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>38714000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>39350000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>31002600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>32658700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>39514400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>35808100</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>30124200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>24</v>
+      <c r="D47" s="3">
+        <v>138600</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>24</v>
@@ -4975,11 +5080,11 @@
       <c r="I47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" s="3">
         <v>841800</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>24</v>
@@ -4996,330 +5101,339 @@
       <c r="P47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R47" s="3">
         <v>7700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>175200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>10200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>10100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>11500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>15300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>16100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>18600</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>21600</v>
       </c>
       <c r="AC47" s="3">
         <v>21600</v>
       </c>
       <c r="AD47" s="3">
+        <v>21600</v>
+      </c>
+      <c r="AE47" s="3">
         <v>598100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>285200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>28800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>32400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>361000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>32700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>34600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>34800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>54100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>35600</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>34600</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>32200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>34400</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1029900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1023500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1028400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1039400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1029500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1006000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1025100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1055000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1056200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1031300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1043000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1040900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1083800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1057800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1055400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1064100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1103500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1096000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1116600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1111100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1146700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1195200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1193800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1180500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1197600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1264200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1261500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1271100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>764200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>765800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>772700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>787700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>793700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>794600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>799900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>800400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>779900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>750600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>733200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>701000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4937700</v>
+      </c>
+      <c r="E49" s="3">
         <v>4929700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4916700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4873200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4876500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4904500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4923000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3699300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3689600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3650700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3684900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3684300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3683000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3696000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3680600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3642100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3633600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3651400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3553200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3537400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3548500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3546600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3553800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3542200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3525200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3406000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3419400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3382200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3394500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3379000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3248100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3242200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3129900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3138600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2997000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2444600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>2361200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2321500</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2205300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2252300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5440,8 +5554,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5562,130 +5679,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1217700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1159000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1113100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1084900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1000900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1005000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>957800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1028600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>909200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1021700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1003400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1360300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>932800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>968800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3565700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3514500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3517100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3406700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3316100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3280700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3324000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2900600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2900700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2835900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2860000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2982900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2991900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2954800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3101500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3098700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3070500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3069900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>3069500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1383700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1363800</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1359400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1344600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1234800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1220600</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1225500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5806,130 +5929,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>63193300</v>
+      </c>
+      <c r="E54" s="3">
         <v>64484200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>84639400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>54320800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>53369300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>56448600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>64096700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>49511400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>54362700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>64181600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>57069400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>49323600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>50971000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>59881800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>54453000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>46364700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>63068200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>72068100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>59102600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>59987200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>48772500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>54407700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>49325900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>42390100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>39165500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>43383400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>49059400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>37714700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>41887700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>48196300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>38806300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>37416700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>38849100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>44065500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>44545500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>35661100</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>37180000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>43855900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>39999400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>34337400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5972,8 +6101,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6016,189 +6146,193 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>162500</v>
+      </c>
+      <c r="E57" s="3">
         <v>136100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>143100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>129000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>169100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>146300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>186400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>145200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>84600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>76800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>67400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>96800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>74800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>85300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>82700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>110200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>81700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>103500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>77800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>141100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>112200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>113900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>111200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>102000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>115500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>132900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>108800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>125500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>156300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>151300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>131800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>135400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>105700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>136800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>112600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>149700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>126500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>137400</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>117800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>243900</v>
+      </c>
+      <c r="E58" s="3">
         <v>102500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>153900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5556800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4909700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1101000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1095100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6150800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>478700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>95300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>119200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>442100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>202100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>94500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>8400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1100</v>
-      </c>
-      <c r="V58" s="3">
-        <v>1200</v>
       </c>
       <c r="W58" s="3">
         <v>1200</v>
@@ -6207,34 +6341,34 @@
         <v>1200</v>
       </c>
       <c r="Y58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z58" s="3">
         <v>1400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1800</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>1001800</v>
       </c>
       <c r="AB58" s="3">
         <v>1001800</v>
       </c>
       <c r="AC58" s="3">
+        <v>1001800</v>
+      </c>
+      <c r="AD58" s="3">
         <v>1001600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4538000</v>
-      </c>
-      <c r="AE58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AF58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AG58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH58" s="3">
         <v>1206000</v>
-      </c>
-      <c r="AH58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AI58" s="3" t="s">
         <v>24</v>
@@ -6251,8 +6385,8 @@
       <c r="AM58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AN58" s="3">
-        <v>0</v>
+      <c r="AN58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AO58" s="3">
         <v>0</v>
@@ -6260,347 +6394,356 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45465200</v>
+      </c>
+      <c r="E59" s="3">
         <v>48092600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>68753200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>32839100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>32235800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>40989100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>49344900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>29645800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>40285200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>50380700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>44761200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>37971300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>39281400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>48517900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>46727200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>39081800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>55047300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>63016400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>48979400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>49590900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>37952500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>44501800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>39061200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>32216600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>29022800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>33555500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>39387900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>24554100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>32502200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>39009700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>28939600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>28905500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>30277300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>36635500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>37114100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>28174000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>29666200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>36292000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>32818900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>26601500</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>50024900</v>
+      </c>
+      <c r="E60" s="3">
         <v>52019700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>72141500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>41932000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>41278300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>45845400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>54303100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>39372400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>45080000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>54901900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>48097700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41228700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>42767600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>51536100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>46813700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>39166200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>55158700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>63106500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>49084000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>49669900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38094800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>44615200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>39176500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>32329600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>30126600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>34672800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>40522400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>29200900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>32627700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>39166000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>30296900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>29037300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>30412700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>36741200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>37250900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>28286600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>29815900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>36418500</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>32956300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>26719300</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5270800</v>
+      </c>
+      <c r="E61" s="3">
         <v>4295500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4324000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4317300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4295900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3265700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3282300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3297500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3319900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3299800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3317000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3324100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3338900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3320700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2988100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2987600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2987100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2986600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2986100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2985500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2985000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1994300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1994100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1993900</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>1002800</v>
       </c>
       <c r="AB61" s="3">
         <v>1002800</v>
       </c>
       <c r="AC61" s="3">
+        <v>1002800</v>
+      </c>
+      <c r="AD61" s="3">
         <v>1003000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1003400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2002200</v>
-      </c>
-      <c r="AF61" s="3">
-        <v>2002300</v>
       </c>
       <c r="AG61" s="3">
         <v>2002300</v>
       </c>
       <c r="AH61" s="3">
-        <v>2002400</v>
+        <v>2002300</v>
       </c>
       <c r="AI61" s="3">
         <v>2002400</v>
@@ -6612,144 +6755,150 @@
         <v>2002400</v>
       </c>
       <c r="AL61" s="3">
+        <v>2002400</v>
+      </c>
+      <c r="AM61" s="3">
         <v>2002100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2002400</v>
-      </c>
-      <c r="AN61" s="3">
-        <v>2002500</v>
       </c>
       <c r="AO61" s="3">
         <v>2002500</v>
       </c>
       <c r="AP61" s="3">
+        <v>2002500</v>
+      </c>
+      <c r="AQ61" s="3">
         <v>2007700</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1141400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1089100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1051200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1041400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1058300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>991200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>999300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>977000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>990800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>935500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>918900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>893000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>933700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>918700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1664500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1634400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1697100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1782100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1982900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1981100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2022600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2124300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2255300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2257700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2283900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2217100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2169600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2149700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1857900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1781800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1743200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1698200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1698100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1292700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1361000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1419000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1384700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1331800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1225500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1360300</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6870,8 +7019,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6992,8 +7144,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7114,130 +7269,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57162100</v>
+      </c>
+      <c r="E66" s="3">
         <v>58134100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>78246400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47947000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47181300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50593300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>59018600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>44162800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>49815100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>59554900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52749800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>45850800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>47461900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>56188000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>51466300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>43788200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>59842900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>67875200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>54053000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>54636500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>43102400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48733800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>43425900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>36581200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>33413300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>37892700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>43695000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>32354000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>36487800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>42950100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>34042400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>32737900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>34113200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>40036300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>40614300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>31707700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>33203000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>39752800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>36184300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>30087300</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7280,8 +7441,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7402,8 +7564,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7524,8 +7689,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7646,8 +7814,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7768,130 +7939,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>26967400</v>
+      </c>
+      <c r="E72" s="3">
         <v>26668100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25992600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25622400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25240600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24956600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>24335600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>24001200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23622200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>23366100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>22757100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>22455400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>22118000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>21857800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>21333000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>21039000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>20696300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20504500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>20011800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19754800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>19451100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>19307500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18893600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>18644700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18436300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>18416500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>17987600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>17729600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>17500600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>17368600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>16959100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>16741100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>16546600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>15466100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>15060100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>14872400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>14728200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>14717700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>14384700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>14130200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8012,8 +8189,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8134,8 +8314,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8256,130 +8439,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6031200</v>
+      </c>
+      <c r="E76" s="3">
         <v>6350100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6393000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6373800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6188000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5855300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5078100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5348600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4547600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4626700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4319600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3472800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3509100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3693800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2986700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2576500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3225300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4192900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5049600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5350700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5670100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5673900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5900000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>5808900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5752200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5490700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>5364400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5360700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5399900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5246200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4763900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4678800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4735900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4029200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3931200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3953400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3977000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4103100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3815100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4250100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8500,257 +8689,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>978600</v>
+      </c>
+      <c r="E81" s="3">
         <v>1359800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1062000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1013000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>910700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1249500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>963200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>956300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>829300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1184900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>878400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>859400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>776700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1043100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>813100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>779000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>625500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>928500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>694400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>700500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>538200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>810700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>647500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>602100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>411600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>820900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>651600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>582400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>475400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>753700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>558200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>505400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>140900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>643100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>670400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>412600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>265800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>587900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>510900</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>368700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8793,130 +8991,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E83" s="3">
         <v>50700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>50400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>49600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>49200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>49700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>45600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>45800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>46100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>44600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>43000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>42800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>43100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>42800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>136800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>135100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>130500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>129000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>126500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>129100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>126000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>126900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>126700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>131100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>124500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>120600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>117600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>117300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>109400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>103100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>97500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>99000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>99300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>96300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>94800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>87200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>82500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>77600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>78400</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>77600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9037,8 +9239,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9159,8 +9364,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9281,8 +9489,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9403,8 +9614,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9525,130 +9739,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1428000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2238000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1132900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>642300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1439200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1525800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1150300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>824400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1300600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1498100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1032400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>326500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1185700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1404100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>899700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>718100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>912900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>971000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1093700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>121900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>652800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1252200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>706400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>481900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>776600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1118700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>698100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>432800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>732300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1024500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>782300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>149200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>705200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1134900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>430400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>244700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>457200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>827600</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>511300</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>329800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9691,130 +9911,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-50600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-26500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-46700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-34100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-36400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-39400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-58800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-54700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-59600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-54800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-39300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-60900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-50300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-141800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-131700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-144300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-152600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-127400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-129100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-33300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-64300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-37500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-43500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-38600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-43900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-56800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-41700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-40300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-43200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-46500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-41300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-45000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-73300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-65700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>116000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-240800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-211800</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9935,8 +10159,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10057,130 +10284,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-958000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1216300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-676900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1862600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>423200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-555900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1257900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1644400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-217200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1094000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>138300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-216100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-464500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-583400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>108200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1577600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1050700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2495300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2232000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1236400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1148600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1416800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1213800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>264200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>2677700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>603500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-247100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>122200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-999800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-728700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-16500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-452700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-546600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-631700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1033700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-292600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>6597400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-3586200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-6044700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>8763900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10223,130 +10456,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>683200</v>
+      </c>
+      <c r="E96" s="3">
         <v>687100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>629300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>626700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>625800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>628000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>572500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>572600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>575100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>575900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>516300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>515800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>517500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>520600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-432600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-432900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-434300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-437700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-393800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-393200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-396000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-397800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-390700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-391000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-391600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-392900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-342700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-343300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-343400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-344600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-302400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-302600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-278600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-278400</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-253000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-253700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-255800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-257100</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-240500</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-241800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10467,8 +10704,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10589,8 +10829,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10711,370 +10954,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2418600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22043000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>29178500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>164100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5057000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9398900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>13974000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6491500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11115500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5867700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5719800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1903700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9994500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3938100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>6678300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-16302600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8725300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>12714000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1520100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>11184800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6486200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4172200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>6227400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2524100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4926600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-6489100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>10571000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5045900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-7153100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>8433700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>329400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1817700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-7014100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-922100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>8345000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2064700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-7295200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>3042800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>5484300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-9513600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E101" s="3">
         <v>24000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-53700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>17000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-6700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-26300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>26900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-16300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>20300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-44900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-84500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>6700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>20300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-44900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-84500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>6700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-21200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-14300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>46800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>37900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>6900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>20900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-33100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-19500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-12600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-47300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>4000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>34900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>14200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>25500</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>6100</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-22300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>5400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1972700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21063800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>29670000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1062900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3144600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8405000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13812700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7294500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10038800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6245500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6917400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1809600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9269100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4758100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7706500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17207000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-8947600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11196400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2658100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10049100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6978600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3993300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5766800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3308100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1465400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4796100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>11042900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4524000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-7415300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>8727500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1075700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2133800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-6902800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-414900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>7776600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-2098400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-215100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>290300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-71400</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-414500</v>
       </c>
     </row>
